--- a/main/ig/StructureDefinition-event-type.xlsx
+++ b/main/ig/StructureDefinition-event-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T15:09:09+00:00</t>
+    <t>2026-03-13T14:54:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-event-type.xlsx
+++ b/main/ig/StructureDefinition-event-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0-ballot</t>
+    <t>3.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:54:50+00:00</t>
+    <t>2026-03-13T16:20:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-event-type.xlsx
+++ b/main/ig/StructureDefinition-event-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T16:20:59+00:00</t>
+    <t>2026-03-13T16:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-event-type.xlsx
+++ b/main/ig/StructureDefinition-event-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T16:21:24+00:00</t>
+    <t>2026-03-13T16:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-event-type.xlsx
+++ b/main/ig/StructureDefinition-event-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T16:21:37+00:00</t>
+    <t>2026-03-13T16:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
